--- a/Final Sheet Broker.xlsx
+++ b/Final Sheet Broker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FE41E5-485A-4F28-B155-EE945A5D615B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8473DE9F-6471-483E-B5AB-BC55084C7FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -761,34 +761,34 @@
   <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
